--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="railing_systems" sheetId="1" state="visible" r:id="rId1"/>
@@ -291,7 +291,7 @@
     <t xml:space="preserve">1000 mm Glass Panel</t>
   </si>
   <si>
-    <t xml:space="preserve">FP-1000-TM, FP-1266-SM, UC-102-TM, UC-117-SM</t>
+    <t xml:space="preserve">UC-102-TM, UC-117-SM</t>
   </si>
   <si>
     <t>G-H1000-W500-U1</t>
